--- a/sum.var_AMR_EHPAD_FQ_R.xlsx
+++ b/sum.var_AMR_EHPAD_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -74,6 +74,15 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_EHPAD_FQ_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
     <t xml:space="preserve">veto_by_AC</t>
   </si>
   <si>
@@ -83,6 +92,54 @@
     <t xml:space="preserve">veto_by_carni</t>
   </si>
   <si>
+    <t xml:space="preserve">tx_possession_chats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_porcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_veaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i007b_part_agribio_surf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_EHPAD_FQ_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_EHPAD_FQ_R.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_i041_pib_hab</t>
+  </si>
+  <si>
     <t xml:space="preserve">prescri_9_inv</t>
   </si>
   <si>
@@ -92,43 +149,7 @@
     <t xml:space="preserve">couv_creche</t>
   </si>
   <si>
-    <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_porcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_veaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i007b_part_agribio_surf</t>
+    <t xml:space="preserve">pop_75_plus_prop</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -611,1433 +632,1706 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00861316748991747</v>
+        <v>-0.00997448175271144</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0183129920200847</v>
+        <v>-0.0332116974675727</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0296401898394678</v>
+        <v>0.00673395387442586</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00913985715637853</v>
+        <v>-0.0236791454821986</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0618505549254476</v>
+        <v>-0.0757500947291418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0944306379323188</v>
+        <v>0.0568064656086319</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0316848661216002</v>
+        <v>-0.0519636488636131</v>
       </c>
       <c r="I2" t="n">
-        <v>0.118334598540654</v>
+        <v>0.10036063159044</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0739303444462348</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0808805183696352</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.126331094334832</v>
+        <v>-0.136759865392762</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0462677646904056</v>
+        <v>-0.0501690072424326</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.117745358345468</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0868256264433057</v>
+        <v>-0.0899670434204568</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0739359745858722</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0418326164672591</v>
+        <v>-0.0500340516551097</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.110143596600073</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0380341417910446</v>
+        <v>-0.0580919365243204</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.11100233628658</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="U2" t="n">
-        <v>0.230236909170794</v>
+        <v>-0.00997448175271144</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0823143588861929</v>
+        <v>-0.0057397080210425</v>
       </c>
       <c r="W2" t="n">
-        <v>0.236671747252345</v>
+        <v>-0.0117322731793835</v>
       </c>
       <c r="X2" t="n">
-        <v>2.26872850114347</v>
+        <v>0.154001140422901</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.126337084384816</v>
+        <v>0.0582695830019245</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0106530722753479</v>
+        <v>0.160323399740883</v>
       </c>
       <c r="AA2" t="n">
-        <v>-13.3529564156964</v>
+        <v>-12.3303494649166</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.90745507079561</v>
+        <v>0.375555392934203</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.1071085687536</v>
+        <v>0.357498405731887</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.849123408081716</v>
+        <v>0.152621661124171</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0455634860050897</v>
+        <v>-0.346688833462624</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.60285402162579</v>
+        <v>0.235349613528001</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.374138084945238</v>
+        <v>-0.209548982113039</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.353223446885017</v>
+        <v>0.00239386743473404</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.144126203811803</v>
+        <v>-0.00997448175271144</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.358907732811541</v>
+        <v>2.46131616730103</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.245022510851497</v>
+        <v>-2.19227167052624</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.234897277063685</v>
+        <v>-0.14689466098425</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.000154612909904424</v>
+        <v>0.464358721866095</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11.0218902694913</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.00997448175271144</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0711842396775379</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.84448446462987</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.102157056829545</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.010521087269544</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.00508228708977854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.050626667646246</v>
+        <v>-0.0593137267948623</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0326209626152758</v>
+        <v>-0.0269866252159834</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0513559452437519</v>
+        <v>-0.0626853491315937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0439384436706734</v>
+        <v>0.0667609974418947</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.00448709604872314</v>
+        <v>0.00896430553400415</v>
       </c>
       <c r="G3" t="n">
-        <v>0.155611260369426</v>
+        <v>0.0780798483358838</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00671658762832956</v>
+        <v>0.0110822982171971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00396897096962525</v>
+        <v>0.0352159793973484</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.193650415987976</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0663386995975042</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="L3" t="n">
-        <v>0.058074531431422</v>
+        <v>0.0674197177529147</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.00219064590148438</v>
+        <v>-0.0113250537682787</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0319406849641082</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.00865166534643926</v>
+        <v>-0.0164060544761927</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0191715108031145</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0217992432396014</v>
+        <v>0.0264843564568429</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0176198556324311</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0129089704823069</v>
+        <v>0.0187351769509707</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0185906677122629</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0296793023108517</v>
+        <v>-0.0593137267948623</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.951449865110641</v>
+        <v>-0.00594697343484887</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0094935971373948</v>
+        <v>0.00718843060368204</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.08665664329034</v>
+        <v>-0.0271665153679097</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.430309179377308</v>
+        <v>-0.770302815554919</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0196594340040168</v>
+        <v>0.00687099960299616</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.50229226552274</v>
+        <v>3.17771325978908</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.76589111085271</v>
+        <v>0.44603511539236</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.99459057903352</v>
+        <v>0.420761142313532</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.83287236119696</v>
+        <v>0.117825175411432</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.907452385504001</v>
+        <v>-0.603686124644861</v>
       </c>
       <c r="AF3" t="n">
-        <v>-7.73433523190195</v>
+        <v>0.323806812980551</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.446086335625506</v>
+        <v>-0.671327616035061</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.420904381119468</v>
+        <v>-0.0109444588619368</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.112689293688101</v>
+        <v>-0.0593137267948623</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.606735432624122</v>
+        <v>-1.78849019467855</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.321528019022092</v>
+        <v>0.594774917323201</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.667244727759906</v>
+        <v>-1.71738724827605</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0116617964847218</v>
+        <v>-0.472378788154204</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-5.42457052529447</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.0593137267948623</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.124494038406793</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-2.09043037842764</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.430405702605618</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.0209620918427937</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.00960011029148658</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.044546817006792</v>
+        <v>-0.0423580963653664</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0431439505326432</v>
+        <v>0.00779730675007682</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.12742392822722</v>
+        <v>-0.0839658046014768</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.164988773584968</v>
+        <v>-0.160573643927154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0123303057206549</v>
+        <v>0.0116350506174326</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.123279895751945</v>
+        <v>-0.169554384362192</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0231232858992188</v>
+        <v>-0.0181058995709713</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.335720032881265</v>
+        <v>-0.278648268623139</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.451954644630813</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.213940388715841</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.10631548506074</v>
+        <v>-0.0837003183939476</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0992612630737609</v>
+        <v>-0.0988475340227592</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.146963647127964</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0653042424768965</v>
+        <v>-0.0466720427614512</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0166225096458366</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.050457255080244</v>
+        <v>0.0503303137154591</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0924826797171393</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0110054980283653</v>
+        <v>-0.00749851703955117</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0870444298965883</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.248208181555572</v>
+        <v>-0.0423580963653664</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0283721447522985</v>
+        <v>-0.00184761400226204</v>
       </c>
       <c r="W4" t="n">
-        <v>0.258678434466207</v>
+        <v>-0.0100046443402444</v>
       </c>
       <c r="X4" t="n">
-        <v>3.96224194733424</v>
+        <v>0.238507466780687</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.187676221275499</v>
+        <v>-0.0055179876751338</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0465284622232639</v>
+        <v>0.265749097758507</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.79675715265322</v>
+        <v>-3.63618198377684</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.89793942205405</v>
+        <v>1.08459192358979</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.91888695042271</v>
+        <v>1.08405563486571</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0718485454466312</v>
+        <v>1.69130769280195</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.48230387877899</v>
+        <v>2.74556373901538</v>
       </c>
       <c r="AF4" t="n">
-        <v>-44.0717037422678</v>
+        <v>0.75630921144054</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.08934863133995</v>
+        <v>2.08339580005781</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.09202055731891</v>
+        <v>-0.00656637404658737</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.69697886753316</v>
+        <v>-0.0423580963653664</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.76336374023148</v>
+        <v>-4.31875399729239</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.738634839353714</v>
+        <v>3.56540005694909</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.05335552203451</v>
+        <v>-0.782589675263861</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.00780540703904721</v>
+        <v>-1.41801144666476</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-42.063917768553</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.0423580963653664</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.0654341902052057</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.40883248308577</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.0988875903309765</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.041946136308274</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.00639467520062348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.054475241028148</v>
+        <v>-0.0480727916411618</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0964445128665869</v>
+        <v>-0.122014764713604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0652960270327491</v>
+        <v>-0.0980898804713043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0288416298067512</v>
+        <v>-0.0460995270754599</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0826278663968937</v>
+        <v>-0.0856219006310501</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0431582941829819</v>
+        <v>-0.114016310368139</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0876436639967819</v>
+        <v>-0.0943666974336294</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.010591224878537</v>
+        <v>-0.046366232871423</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.133073807124284</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0387022397834397</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0219572900805837</v>
+        <v>-0.0457414901501482</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.014947197697644</v>
+        <v>-0.026573481692435</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0607279022494005</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0687780592145559</v>
+        <v>-0.0647205616522289</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0395682787955851</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.019754517988177</v>
+        <v>-0.0218776303200323</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.064253213480474</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0877586553697194</v>
+        <v>-0.094704517426158</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0660853703502294</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.224450493497355</v>
+        <v>-0.0480727916411618</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.702980093464589</v>
+        <v>0.0108436371775343</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.216611709309765</v>
+        <v>0.0064511956297064</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.823797532930937</v>
+        <v>-0.240200751296639</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.871861907402698</v>
+        <v>-0.602380310114915</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.0318871052066737</v>
+        <v>-0.239853211250507</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.0105838439942</v>
+        <v>12.8592769993275</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.03411024295447</v>
+        <v>-0.480525696225354</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.732963782034703</v>
+        <v>-0.491243416945087</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.41797289246903</v>
+        <v>-0.517661915067306</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.461480865327236</v>
+        <v>-0.268031660005875</v>
       </c>
       <c r="AF5" t="n">
-        <v>-8.74828496441936</v>
+        <v>-0.416594915570839</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.48291206265778</v>
+        <v>-0.311494422645666</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.49370513919715</v>
+        <v>-0.0482426004035456</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.50347965976719</v>
+        <v>-0.0480727916411618</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.271997218981367</v>
+        <v>-3.27804295023073</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.414598368563884</v>
+        <v>0.103643179064499</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.239269869106092</v>
+        <v>-1.31587084830012</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.0593785533477566</v>
+        <v>-0.38010878600959</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-6.61747476724499</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.0480727916411618</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.0889789398903094</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.241745236060253</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.805735820374807</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.0302881325843596</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.00829966907346026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0111939802172769</v>
+        <v>0.00300839854680181</v>
       </c>
       <c r="C6" t="n">
-        <v>0.104774414094836</v>
+        <v>0.110123897161324</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0486921789422257</v>
+        <v>0.0594823394641421</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0330542854772905</v>
+        <v>0.00138620103745199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0351904977590381</v>
+        <v>-0.0410338671533221</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.188971655655608</v>
+        <v>0.0156302908688696</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0191888842852598</v>
+        <v>-0.00777819389424965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.197351653281297</v>
+        <v>0.183072132285433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0018191669464986</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.10514076330124</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.075073448104575</v>
+        <v>0.0722057873717832</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0498425094487324</v>
+        <v>0.0581279308629707</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0429377771407168</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0130550374147194</v>
+        <v>-0.0139516952096968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0814110793482235</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0271531331113151</v>
+        <v>-0.0395915370136168</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0213278991632336</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0266988959479993</v>
+        <v>-0.0130612761644817</v>
       </c>
       <c r="T6" t="n">
-        <v>0.017381995935277</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.125315141810005</v>
+        <v>0.00300839854680181</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.533253963938384</v>
+        <v>0.0145774880585199</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.111205268016524</v>
+        <v>-0.000123590283420022</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.02826844933859</v>
+        <v>-0.0748923204047765</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.20638904583026</v>
+        <v>-0.423678741868557</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0199497067482329</v>
+        <v>-0.0594431157486579</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.06386167733992</v>
+        <v>-2.61132807038946</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.727581913604155</v>
+        <v>0.137839947010808</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.6806897509786</v>
+        <v>0.13637941094463</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.757805216853566</v>
+        <v>-0.122399969203203</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.112658406002476</v>
+        <v>-0.388364951192247</v>
       </c>
       <c r="AF6" t="n">
-        <v>-18.5609461478032</v>
+        <v>-0.0224633016088872</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.135540512914882</v>
+        <v>-0.595670602562299</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.13464575873053</v>
+        <v>-0.0287033067680863</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.124253463184203</v>
+        <v>0.00300839854680181</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.38154892670527</v>
+        <v>0.647163158559724</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0273898763368545</v>
+        <v>-3.1904011933925</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.564708653492967</v>
+        <v>-0.453595963951475</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0339212806169313</v>
+        <v>0.622946781722748</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-15.8994468340273</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.00300839854680181</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.0879917342022967</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-2.76898226499257</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.190653634970529</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.0118321019448495</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.00593181281709199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0828896819662445</v>
+        <v>0.0677420175858707</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0517940425682514</v>
+        <v>0.0554788106625309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.071714874848011</v>
+        <v>0.0614207298724778</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0184747916864388</v>
+        <v>-0.0145088813068838</v>
       </c>
       <c r="F7" t="n">
-        <v>0.113431907201674</v>
+        <v>0.110606121684165</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33951630535917</v>
+        <v>0.250285857549249</v>
       </c>
       <c r="H7" t="n">
-        <v>0.101418400848082</v>
+        <v>0.0918115939259928</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0680500028384321</v>
+        <v>0.0601744798308835</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.127591808649287</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0700382439093241</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0950962118646464</v>
+        <v>0.103548025235894</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0040114856575273</v>
+        <v>0.00202098858221799</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0738353300350503</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.11031703489954</v>
+        <v>0.110979265869809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0317436369380914</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0161942985620362</v>
+        <v>0.00273469106055817</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1031726582803</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="S7" t="n">
-        <v>0.102217487122142</v>
+        <v>0.0951759245750315</v>
       </c>
       <c r="T7" t="n">
-        <v>0.107749494339726</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.341366742677719</v>
+        <v>0.0677420175858707</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0677961903681076</v>
+        <v>-0.000652098137484839</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.367616315867778</v>
+        <v>-0.0064557992462484</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.95820065968298</v>
+        <v>-0.283628703906132</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.588958876653253</v>
+        <v>0.138826687668009</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0452964285657324</v>
+        <v>-0.309927730022684</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5.48000756276893</v>
+        <v>-4.93482380993126</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13254732195702</v>
+        <v>0.418246721515095</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.2558087108948</v>
+        <v>0.424361583032095</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.44868986368902</v>
+        <v>0.289059744010996</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.53101306628933</v>
+        <v>0.308994584925497</v>
       </c>
       <c r="AF7" t="n">
-        <v>-33.7492790849095</v>
+        <v>0.159101834134017</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.41812233257602</v>
+        <v>0.197995368697023</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.423717356824562</v>
+        <v>-0.0626469474552824</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.291364067432138</v>
+        <v>0.0677420175858707</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.314649313057139</v>
+        <v>1.12134033295021</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.159506951944619</v>
+        <v>-5.94298722785559</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.217469425638462</v>
+        <v>2.15545868450043</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0766525316851343</v>
+        <v>1.54602068082667</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-32.1995523411849</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.0677420175858707</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.130900303696153</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.36750673911582</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.563513299647262</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.0501937303954304</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.0185588523633794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0268004152201697</v>
+        <v>0.051536860950639</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0933110340800905</v>
+        <v>-0.134831925330972</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.096915276563401</v>
+        <v>-0.106665696028367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0473413618712882</v>
+        <v>-0.00210520011203225</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.022017329387451</v>
+        <v>-0.0041952574902393</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.117054686263068</v>
+        <v>-0.11590073157777</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0563680217864088</v>
+        <v>-0.0493917054781802</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0561936176075413</v>
+        <v>-0.0883645155060498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.318115857618149</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0238939566761317</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0546039836988301</v>
+        <v>-0.0715951342108236</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0494835030365521</v>
+        <v>-0.0463280683589995</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0192992710616377</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0719851990011906</v>
+        <v>0.0861825699207249</v>
       </c>
       <c r="P8" t="n">
-        <v>0.263702897723594</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0283925238251064</v>
+        <v>0.0241502037875185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0819104900657102</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0504008979872673</v>
+        <v>-0.0423401208623003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0904384546906766</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00194161246930321</v>
+        <v>0.051536860950639</v>
       </c>
       <c r="V8" t="n">
-        <v>2.41769866965332</v>
+        <v>-0.00203471874096844</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0299675097204871</v>
+        <v>-0.00704514598014381</v>
       </c>
       <c r="X8" t="n">
-        <v>0.104420280308834</v>
+        <v>-0.0196716387334885</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.786668372752808</v>
+        <v>1.71905337412741</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.102839961643671</v>
+        <v>-0.0529446881570243</v>
       </c>
       <c r="AA8" t="n">
-        <v>-12.3746677963614</v>
+        <v>-9.01272307721351</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.0724465304478</v>
+        <v>-1.96214937859133</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.62601451656845</v>
+        <v>-1.89546618886632</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.82902623371896</v>
+        <v>-1.89651190208578</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27252545407136</v>
+        <v>-1.22021097105653</v>
       </c>
       <c r="AF8" t="n">
-        <v>-17.6551884293156</v>
+        <v>-1.22631695627796</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.97141411135747</v>
+        <v>-0.810419476847576</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1.90329344295998</v>
+        <v>-0.0360635327910034</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.9045098091507</v>
+        <v>0.051536860950639</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-1.2286983281504</v>
+        <v>11.0611048510848</v>
       </c>
       <c r="AK8" t="n">
-        <v>-1.214980731218</v>
+        <v>-8.13657157043532</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.81115321078737</v>
+        <v>1.89965622981696</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.0391757470512932</v>
+        <v>1.2231669853248</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-14.3772288344109</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.051536860950639</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.623368914024887</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.283112944514979</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.868083983240932</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.103648576807794</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.0301335771134524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0548828150547752</v>
+        <v>-0.0452802345411879</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0908154063833623</v>
+        <v>0.0694253778846952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0252075987398701</v>
+        <v>0.0346589884140389</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0848088025164889</v>
+        <v>0.111605333198221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0964001092563769</v>
+        <v>0.0962525363404283</v>
       </c>
       <c r="G9" t="n">
-        <v>0.114235322202173</v>
+        <v>0.153427391633997</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0864430334074828</v>
+        <v>0.0855536155303945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0855671406191385</v>
+        <v>0.0504734259398501</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.24990238220054</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.110023924925726</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0666041788608702</v>
+        <v>0.067673495916023</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.00486189894067004</v>
+        <v>-0.0108437631294407</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0659590130166441</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0414201417745825</v>
+        <v>0.0415623718171625</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.01794653131492</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0152674888601581</v>
+        <v>-0.0027053805893549</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0389292554061677</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0913168010868526</v>
+        <v>0.09066077539429</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0412352291088098</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1161913209497</v>
+        <v>-0.0452802345411879</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.420726256705248</v>
+        <v>-0.000969293831558328</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0971881326782373</v>
+        <v>-0.00545927080555194</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.50611308851017</v>
+        <v>0.120325299563882</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.572882338993338</v>
+        <v>-0.314908419026853</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.0503208269908725</v>
+        <v>0.0986064075879345</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.434902874457403</v>
+        <v>-0.624784079803963</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.24924605648462</v>
+        <v>1.05828541957378</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.443163248061412</v>
+        <v>1.06438261422827</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.213569909240211</v>
+        <v>0.785942009562261</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.197327402480634</v>
+        <v>0.487882730365099</v>
       </c>
       <c r="AF9" t="n">
-        <v>-40.1872934443512</v>
+        <v>0.697195612240213</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.06031623609118</v>
+        <v>-0.0374455911788562</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.06679185937841</v>
+        <v>-0.0315474910081037</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.783406938003477</v>
+        <v>-0.0452802345411879</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.492361632854778</v>
+        <v>-1.67028852900829</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.692257270079792</v>
+        <v>-0.0109312412913779</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.0434407178522241</v>
+        <v>-0.191921675231057</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.0397057062642703</v>
+        <v>-0.336248048840461</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-38.3424138223202</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.0452802345411879</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.085804112752481</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.12932288721738</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.56047013214129</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.0496410442958685</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.000208184884516435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00291910635945121</v>
+        <v>-0.00344133204854236</v>
       </c>
       <c r="C10" t="n">
-        <v>0.18141548386084</v>
+        <v>0.194361998892864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.120517802794189</v>
+        <v>0.0975994435577037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0242648862067142</v>
+        <v>0.0233719976102421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0336230581140576</v>
+        <v>0.0395856823912233</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0836432431409338</v>
+        <v>0.0123800376221514</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0604342012412549</v>
+        <v>0.0705558338791445</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0706131318802972</v>
+        <v>0.0849547857042242</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0555497938658357</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0326720029776551</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.102308694604747</v>
+        <v>0.108725795381303</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0653162694963985</v>
+        <v>0.0660182326205712</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.00393922007604023</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0399193948643372</v>
+        <v>0.0307882196430586</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0493637376076021</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0251370803361067</v>
+        <v>0.013325731189545</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0365736044705065</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0520397781956754</v>
+        <v>0.0637311713530358</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0318832664375834</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0180891895563711</v>
+        <v>-0.00344133204854236</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.359828122135489</v>
+        <v>-0.00540575234929896</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01835404692612</v>
+        <v>-0.00579879783185996</v>
       </c>
       <c r="X10" t="n">
-        <v>0.721599339885482</v>
+        <v>-0.0342589796517672</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.306905751334375</v>
+        <v>-0.317730159419209</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0038890512293674</v>
+        <v>-0.0346914560561887</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.221877128799</v>
+        <v>9.18564175834393</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.09955219383227</v>
+        <v>0.0993371854900619</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.109406110906727</v>
+        <v>0.0648298521035288</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.785236151216309</v>
+        <v>0.120572232824682</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.806273296794517</v>
+        <v>-0.117960350491315</v>
       </c>
       <c r="AF10" t="n">
-        <v>21.2408997617485</v>
+        <v>0.0824821535077846</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0878669016985042</v>
+        <v>0.322043412432475</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0527545314252715</v>
+        <v>-0.0161333980051841</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.110002981287053</v>
+        <v>-0.00344133204854236</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.100761348093358</v>
+        <v>-3.36054905774655</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0750545205261724</v>
+        <v>0.125640023711585</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.299579447540225</v>
+        <v>-1.05862112080309</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.0176216596940702</v>
+        <v>-0.969569942067806</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.4716391934634</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.00344133204854236</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.0682606175468987</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.338891745096766</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.255688366175892</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.000487602492993006</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.0154679259900934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0101240714816375</v>
+        <v>0.0148543968445671</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0951574267488099</v>
+        <v>0.147380940790155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0335567368423866</v>
+        <v>0.0860160295965499</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0164551145257838</v>
+        <v>0.02995211991031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00780615483989424</v>
+        <v>0.00953556340121431</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0971462052884647</v>
+        <v>-0.0663141535071389</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0157659412790782</v>
+        <v>0.0296954906944263</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0705525729203491</v>
+        <v>0.0158617624856274</v>
       </c>
       <c r="J11" t="n">
-        <v>0.38173871918007</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0774794106161145</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0296589153009829</v>
+        <v>0.0468517688481327</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0883529873226057</v>
+        <v>0.109958567821692</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0439406748189093</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0324170708373091</v>
+        <v>0.0211958266043548</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0492797520250096</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00536959394916804</v>
+        <v>-0.000646349904212877</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0337209410800998</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0137392681072874</v>
+        <v>0.0240534255699838</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0265724264376512</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0523949655042163</v>
+        <v>0.0148543968445671</v>
       </c>
       <c r="V11" t="n">
-        <v>0.147844667455911</v>
+        <v>0.0169332582755317</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0598229723300898</v>
+        <v>0.0533113040488226</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.58720382750977</v>
+        <v>-0.0354567410752362</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.477227071488994</v>
+        <v>0.128949509529747</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0324091388890802</v>
+        <v>-0.0422757744771231</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.93076072201193</v>
+        <v>6.42513956495643</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.27412376874592</v>
+        <v>-0.280465339930393</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.53463775092322</v>
+        <v>-0.315517269456471</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.842423802641169</v>
+        <v>-0.268724626977033</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.887510220873973</v>
+        <v>-0.489446482450284</v>
       </c>
       <c r="AF11" t="n">
-        <v>73.836852084884</v>
+        <v>-0.198475120765655</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.278313881553092</v>
+        <v>-0.48313178901756</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.316322495801499</v>
+        <v>0.0595370092343964</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.273163608669828</v>
+        <v>0.0148543968445671</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.518269530698474</v>
+        <v>-1.42640909208072</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.185309946919603</v>
+        <v>5.91211095973774</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.505204924238184</v>
+        <v>-0.895613718645758</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0737223600770482</v>
+        <v>-0.823422918814776</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>64.7608500031866</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0148543968445671</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.0794686588701281</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.60245407764797</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.482211586012499</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.0316327784762719</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.00888449742549417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B12" t="n">
-        <v>0.147024197001679</v>
+        <v>0.132144077720306</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0472853302454616</v>
+        <v>0.0627569214130735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.15994964345674</v>
+        <v>0.16928729582152</v>
       </c>
       <c r="E12" t="n">
-        <v>0.30483309621511</v>
+        <v>0.181161651205074</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0216068661445064</v>
+        <v>0.0151993913420284</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00492305245927262</v>
+        <v>-0.049942846229566</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0800725918839381</v>
+        <v>0.0663592388653425</v>
       </c>
       <c r="I12" t="n">
-        <v>0.126444991841773</v>
+        <v>0.12082021118173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.468790220246551</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0214175220488185</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0593349481251918</v>
+        <v>0.0523986716894069</v>
       </c>
       <c r="M12" t="n">
-        <v>0.126866116349198</v>
+        <v>0.131205113193585</v>
       </c>
       <c r="N12" t="n">
-        <v>0.249495448342264</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0759085290894156</v>
+        <v>0.0571106148616265</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00298579174349232</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0231486239148022</v>
+        <v>0.0331111192044257</v>
       </c>
       <c r="R12" t="n">
-        <v>0.115736157752528</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="S12" t="n">
-        <v>0.068689399115839</v>
+        <v>0.0506071158844021</v>
       </c>
       <c r="T12" t="n">
-        <v>0.109250040417882</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="U12" t="n">
-        <v>0.117213334328821</v>
+        <v>0.132144077720306</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03692572276799</v>
+        <v>-0.0158690518044377</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0954164633052321</v>
+        <v>-0.00954756689330399</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2146847521016</v>
+        <v>0.10215117539764</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27563193890262</v>
+        <v>1.02430888453424</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.065230270652153</v>
+        <v>0.0779898973230106</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.0549294668418</v>
+        <v>10.3825789897294</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.77431735353736</v>
+        <v>-1.96187907500934</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.17987068207479</v>
+        <v>-1.89482506440636</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.27048364924756</v>
+        <v>-1.59565512176468</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.653225780721063</v>
+        <v>-1.18205595693551</v>
       </c>
       <c r="AF12" t="n">
-        <v>76.3178647237378</v>
+        <v>-1.22766947552045</v>
       </c>
       <c r="AG12" t="n">
-        <v>-1.93290812936691</v>
+        <v>-1.35410658786014</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.86585837321694</v>
+        <v>0.168168106349812</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.57195428096921</v>
+        <v>0.132144077720306</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-1.17509471829072</v>
+        <v>4.24082559502784</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1.20618808689521</v>
+        <v>6.72187461778694</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.37194950037746</v>
+        <v>3.20570944017448</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.200001542347917</v>
+        <v>1.13064796511604</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>69.5078139826724</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.132144077720306</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.0495522387392417</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.456645557777998</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.25678752951199</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.0696894773037612</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.0122694085372572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0619685313016773</v>
+        <v>-0.0608450885043526</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.28740865178688</v>
+        <v>-0.330280240826589</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.148287848395769</v>
+        <v>-0.163792050368117</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.218612594880803</v>
+        <v>-0.167271902499466</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0790250567596117</v>
+        <v>-0.0851775313067445</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0456164931208141</v>
+        <v>-0.0508814655739771</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.132842034198897</v>
+        <v>-0.133451925871853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.197273041683526</v>
+        <v>-0.237554391414924</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.14377104371044</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.137448548593002</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.17694307511745</v>
+        <v>-0.181026454047777</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.117377094933945</v>
+        <v>-0.123243924866692</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.198032071580457</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.129352739570458</v>
+        <v>-0.116101471196711</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.15229813258169</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0233630774577472</v>
+        <v>-0.0352814659320229</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.18211137205329</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.127013614985708</v>
+        <v>-0.127267221710903</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.17896943854647</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0775044768823281</v>
+        <v>-0.0608450885043526</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.812713452529466</v>
+        <v>-0.00388917318968417</v>
       </c>
       <c r="W13" t="n">
-        <v>0.106129447331348</v>
+        <v>-0.010783841722055</v>
       </c>
       <c r="X13" t="n">
-        <v>5.14793488469238</v>
+        <v>0.10029056827084</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.490045091882256</v>
+        <v>-0.63488960520175</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.0335008419885579</v>
+        <v>0.129596173698853</v>
       </c>
       <c r="AA13" t="n">
-        <v>-9.21728994789245</v>
+        <v>-8.88016008611467</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.29348539541788</v>
+        <v>1.06512778425032</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86124116167464</v>
+        <v>1.04478329645459</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.348184368883628</v>
+        <v>1.2436250193625</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.267292948291234</v>
+        <v>1.07400427593327</v>
       </c>
       <c r="AF13" t="n">
-        <v>-10.2914395470274</v>
+        <v>0.837274531912688</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.05412914974397</v>
+        <v>1.8697104870729</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.03512155949341</v>
+        <v>0.010749126320787</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.2387924699854</v>
+        <v>-0.0608450885043526</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07163855021185</v>
+        <v>-3.68921628388639</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.816462898155666</v>
+        <v>2.44971914892797</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.8674644854647</v>
+        <v>-0.698329443036231</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0123533926681638</v>
+        <v>-0.587401204304756</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-10.837588555778</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.0608450885043526</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.0127727968714012</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.29827503179176</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.513037522362324</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.0347804888684874</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.00141794201922911</v>
       </c>
     </row>
   </sheetData>

--- a/sum.var_AMR_EHPAD_FQ_R.xlsx
+++ b/sum.var_AMR_EHPAD_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
     <t xml:space="preserve">AMR_EHPAD_FQ_R.1</t>
@@ -653,10 +656,13 @@
       <c r="AT1" t="s">
         <v>45</v>
       </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="n">
         <v>-0.00997448175271144</v>
@@ -716,87 +722,90 @@
         <v>-0.114851315499916</v>
       </c>
       <c r="U2" t="n">
+        <v>0.0783652775785313</v>
+      </c>
+      <c r="V2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>-0.0057397080210425</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-0.0117322731793835</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.154001140422901</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0.0582695830019245</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>0.160323399740883</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>-12.3303494649166</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.375555392934203</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.357498405731887</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.152621661124171</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>-0.346688833462624</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>0.235349613528001</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>-0.209548982113039</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>0.00239386743473404</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>2.46131616730103</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>-2.19227167052624</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>-0.14689466098425</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>0.464358721866095</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>11.0218902694913</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>0.0711842396775379</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.84448446462987</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>0.102157056829545</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>0.010521087269544</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>-0.00508228708977854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0593137267948623</v>
@@ -856,87 +865,90 @@
         <v>0.0175382891813646</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.0332510477570974</v>
+      </c>
+      <c r="V3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>-0.00594697343484887</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.00718843060368204</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>-0.0271665153679097</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>-0.770302815554919</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.00687099960299616</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>3.17771325978908</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.44603511539236</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.420761142313532</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.117825175411432</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>-0.603686124644861</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>0.323806812980551</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>-0.671327616035061</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>-0.0109444588619368</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>-1.78849019467855</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>0.594774917323201</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>-1.71738724827605</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>-0.472378788154204</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>-5.42457052529447</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>-0.124494038406793</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>-2.09043037842764</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>-0.430405702605618</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>-0.0209620918427937</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>0.00960011029148658</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0423580963653664</v>
@@ -996,87 +1008,90 @@
         <v>-0.0732747438842462</v>
       </c>
       <c r="U4" t="n">
+        <v>0.114914367516149</v>
+      </c>
+      <c r="V4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>-0.00184761400226204</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-0.0100046443402444</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>0.238507466780687</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.0055179876751338</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>0.265749097758507</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>-3.63618198377684</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>1.08459192358979</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>1.08405563486571</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>1.69130769280195</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>2.74556373901538</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>0.75630921144054</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>2.08339580005781</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>-0.00656637404658737</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>-4.31875399729239</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>3.56540005694909</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>-0.782589675263861</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>-1.41801144666476</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>-42.063917768553</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>-0.0654341902052057</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>3.40883248308577</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>0.0988875903309765</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>-0.041946136308274</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>0.00639467520062348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" t="n">
         <v>-0.0480727916411618</v>
@@ -1136,87 +1151,90 @@
         <v>-0.0662767394077226</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0296737136920025</v>
+      </c>
+      <c r="V5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.0108436371775343</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>0.0064511956297064</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-0.240200751296639</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>-0.602380310114915</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.239853211250507</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>12.8592769993275</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>-0.480525696225354</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.491243416945087</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-0.517661915067306</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>-0.268031660005875</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>-0.416594915570839</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>-0.311494422645666</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>-0.0482426004035456</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>-3.27804295023073</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>0.103643179064499</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>-1.31587084830012</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>-0.38010878600959</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>-6.61747476724499</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.0889789398903094</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>0.241745236060253</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>-0.805735820374807</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>-0.0302881325843596</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>0.00829966907346026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" t="n">
         <v>0.00300839854680181</v>
@@ -1276,87 +1294,90 @@
         <v>0.0248295369766438</v>
       </c>
       <c r="U6" t="n">
+        <v>-0.0694984089622275</v>
+      </c>
+      <c r="V6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.0145774880585199</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.000123590283420022</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>-0.0748923204047765</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.423678741868557</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.0594431157486579</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>-2.61132807038946</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>0.137839947010808</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>0.13637941094463</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>-0.122399969203203</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>-0.388364951192247</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>-0.0224633016088872</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>-0.595670602562299</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>-0.0287033067680863</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>0.647163158559724</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>-3.1904011933925</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>-0.453595963951475</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>0.622946781722748</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>-15.8994468340273</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>-0.0879917342022967</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>-2.76898226499257</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>-0.190653634970529</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>0.0118321019448495</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>-0.00593181281709199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="n">
         <v>0.0677420175858707</v>
@@ -1416,87 +1437,90 @@
         <v>0.111511245163811</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0276913164771287</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.000652098137484839</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>-0.0064557992462484</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>-0.283628703906132</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0.138826687668009</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.309927730022684</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>-4.93482380993126</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>0.418246721515095</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>0.424361583032095</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>0.289059744010996</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>0.308994584925497</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>0.159101834134017</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>0.197995368697023</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>-0.0626469474552824</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>1.12134033295021</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>-5.94298722785559</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>2.15545868450043</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>1.54602068082667</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>-32.1995523411849</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>-0.130900303696153</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>-1.36750673911582</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>-0.563513299647262</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>-0.0501937303954304</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>-0.0185588523633794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="n">
         <v>0.051536860950639</v>
@@ -1556,87 +1580,90 @@
         <v>0.0918117366690664</v>
       </c>
       <c r="U8" t="n">
+        <v>0.00189803511554691</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-0.00203471874096844</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.00704514598014381</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-0.0196716387334885</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.71905337412741</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-0.0529446881570243</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>-9.01272307721351</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-1.96214937859133</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-1.89546618886632</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-1.89651190208578</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>-1.22021097105653</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>-1.22631695627796</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>-0.810419476847576</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>-0.0360635327910034</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>11.0611048510848</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>-8.13657157043532</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>1.89965622981696</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>1.2231669853248</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>-14.3772288344109</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>0.623368914024887</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>0.283112944514979</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>0.868083983240932</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>0.103648576807794</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>-0.0301335771134524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0452802345411879</v>
@@ -1696,87 +1723,90 @@
         <v>0.0416848994848347</v>
       </c>
       <c r="U9" t="n">
+        <v>0.0247461477456109</v>
+      </c>
+      <c r="V9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-0.000969293831558328</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>-0.00545927080555194</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.120325299563882</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.314908419026853</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>0.0986064075879345</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>-0.624784079803963</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>1.05828541957378</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>1.06438261422827</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>0.785942009562261</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>0.487882730365099</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>0.697195612240213</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>-0.0374455911788562</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>-0.0315474910081037</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>-1.67028852900829</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>-0.0109312412913779</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>-0.191921675231057</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>-0.336248048840461</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>-38.3424138223202</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.085804112752481</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>-1.12932288721738</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>-0.56047013214129</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>-0.0496410442958685</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>0.000208184884516435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" t="n">
         <v>-0.00344133204854236</v>
@@ -1836,87 +1866,90 @@
         <v>0.0274333514639498</v>
       </c>
       <c r="U10" t="n">
+        <v>-0.0338589119520969</v>
+      </c>
+      <c r="V10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-0.00540575234929896</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>-0.00579879783185996</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.0342589796517672</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>-0.317730159419209</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-0.0346914560561887</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>9.18564175834393</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.0993371854900619</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>0.0648298521035288</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>0.120572232824682</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>-0.117960350491315</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>0.0824821535077846</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>0.322043412432475</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>-0.0161333980051841</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>-3.36054905774655</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>0.125640023711585</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>-1.05862112080309</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>-0.969569942067806</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>20.4716391934634</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.0682606175468987</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>0.338891745096766</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>0.255688366175892</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>0.000487602492993006</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>0.0154679259900934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" t="n">
         <v>0.0148543968445671</v>
@@ -1976,87 +2009,90 @@
         <v>0.0233233898465209</v>
       </c>
       <c r="U11" t="n">
+        <v>-0.134269002145114</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>0.0169332582755317</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.0533113040488226</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>-0.0354567410752362</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>0.128949509529747</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-0.0422757744771231</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>6.42513956495643</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>-0.280465339930393</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-0.315517269456471</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>-0.268724626977033</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>-0.489446482450284</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>-0.198475120765655</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>-0.48313178901756</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>0.0595370092343964</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>-1.42640909208072</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>5.91211095973774</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>-0.895613718645758</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>-0.823422918814776</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>64.7608500031866</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.0794686588701281</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>-1.60245407764797</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>0.482211586012499</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>0.0316327784762719</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>0.00888449742549417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" t="n">
         <v>0.132144077720306</v>
@@ -2116,87 +2152,90 @@
         <v>0.0855989607660336</v>
       </c>
       <c r="U12" t="n">
+        <v>-0.193983119750397</v>
+      </c>
+      <c r="V12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-0.0158690518044377</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>-0.00954756689330399</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.10215117539764</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.02430888453424</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>0.0779898973230106</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>10.3825789897294</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>-1.96187907500934</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-1.89482506440636</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>-1.59565512176468</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>-1.18205595693551</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>-1.22766947552045</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>-1.35410658786014</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>0.168168106349812</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>4.24082559502784</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>6.72187461778694</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>3.20570944017448</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>1.13064796511604</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>69.5078139826724</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>0.0495522387392417</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>-0.456645557777998</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>1.25678752951199</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>0.0696894773037612</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>0.0122694085372572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" t="n">
         <v>-0.0608450885043526</v>
@@ -2256,81 +2295,84 @@
         <v>-0.16932861076034</v>
       </c>
       <c r="U13" t="n">
+        <v>0.187571632441963</v>
+      </c>
+      <c r="V13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>-0.00388917318968417</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>-0.010783841722055</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>0.10029056827084</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>-0.63488960520175</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>0.129596173698853</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>-8.88016008611467</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>1.06512778425032</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>1.04478329645459</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>1.2436250193625</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>1.07400427593327</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>0.837274531912688</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>1.8697104870729</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>0.010749126320787</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>-3.68921628388639</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>2.44971914892797</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>-0.698329443036231</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>-0.587401204304756</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>-10.837588555778</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.0127727968714012</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>3.29827503179176</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>-0.513037522362324</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>-0.0347804888684874</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>-0.00141794201922911</v>
       </c>
     </row>

--- a/sum.var_AMR_EHPAD_FQ_R.xlsx
+++ b/sum.var_AMR_EHPAD_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">log_AMC_EHPAD_tetracyclines</t>
   </si>
   <si>
+    <t xml:space="preserve">log_AMC_EHPAD_tot_except_C3G</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_EHPAD_totale</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
     <t xml:space="preserve">log_AMC_ville_tmp_sulfa</t>
   </si>
   <si>
+    <t xml:space="preserve">log_AMC_ville_tot_except_C3G</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_ville_totale</t>
   </si>
   <si>
@@ -77,6 +83,9 @@
     <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
+    <t xml:space="preserve">prescri_9_inv</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMR_EHPAD_FQ_R.1</t>
   </si>
   <si>
@@ -141,9 +150,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_i041_pib_hab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prescri_9_inv</t>
   </si>
   <si>
     <t xml:space="preserve">medecin_hab</t>
@@ -659,10 +665,16 @@
       <c r="AU1" t="s">
         <v>46</v>
       </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" t="n">
         <v>-0.00997448175271144</v>
@@ -683,129 +695,135 @@
         <v>0.0568064656086319</v>
       </c>
       <c r="H2" t="n">
+        <v>-0.0536803976794544</v>
+      </c>
+      <c r="I2" t="n">
         <v>-0.0519636488636131</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.10036063159044</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.0335610808107989</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.045746548313324</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>-0.136759865392762</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>-0.0501690072424326</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>-0.119218369487267</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>-0.0899670434204568</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>-0.0729740524328948</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>-0.0500340516551097</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
+        <v>-0.110924482615121</v>
+      </c>
+      <c r="T2" t="n">
         <v>-0.11340677064681</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>-0.0580919365243204</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>-0.114851315499916</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0783652775785313</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
+        <v>1.84448446462987</v>
+      </c>
+      <c r="Y2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Z2" t="n">
         <v>-0.0057397080210425</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>-0.0117322731793835</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>0.154001140422901</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>0.0582695830019245</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>0.160323399740883</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>-12.3303494649166</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>0.375555392934203</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>0.357498405731887</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>0.152621661124171</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>-0.346688833462624</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>0.235349613528001</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>-0.209548982113039</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>0.00239386743473404</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>2.46131616730103</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>-2.19227167052624</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>-0.14689466098425</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
         <v>0.464358721866095</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AR2" t="n">
         <v>11.0218902694913</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>-0.00997448175271144</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AT2" t="n">
         <v>0.0711842396775379</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1.84448446462987</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="n">
         <v>0.102157056829545</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
         <v>0.010521087269544</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AW2" t="n">
         <v>-0.00508228708977854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0593137267948623</v>
@@ -826,129 +844,135 @@
         <v>0.0780798483358838</v>
       </c>
       <c r="H3" t="n">
+        <v>0.0176042233387117</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.0110822982171971</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.0352159793973484</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-0.0975259174762126</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.0890607105496024</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.0674197177529147</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>-0.0113250537682787</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.0302138660849762</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>-0.0164060544761927</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.0138953877725435</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0.0264843564568429</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
+        <v>0.0100861804927537</v>
+      </c>
+      <c r="T3" t="n">
         <v>0.0155037622756563</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0187351769509707</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0175382891813646</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>-0.0332510477570974</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
+        <v>-2.09043037842764</v>
+      </c>
+      <c r="Y3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>-0.00594697343484887</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>0.00718843060368204</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>-0.0271665153679097</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>-0.770302815554919</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>0.00687099960299616</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>3.17771325978908</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>0.44603511539236</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>0.420761142313532</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>0.117825175411432</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>-0.603686124644861</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>0.323806812980551</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>-0.671327616035061</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>-0.0109444588619368</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>-1.78849019467855</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AO3" t="n">
         <v>0.594774917323201</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AP3" t="n">
         <v>-1.71738724827605</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>-0.472378788154204</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AR3" t="n">
         <v>-5.42457052529447</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AS3" t="n">
         <v>-0.0593137267948623</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AT3" t="n">
         <v>-0.124494038406793</v>
       </c>
-      <c r="AR3" t="n">
-        <v>-2.09043037842764</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
         <v>-0.430405702605618</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AV3" t="n">
         <v>-0.0209620918427937</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AW3" t="n">
         <v>0.00960011029148658</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0423580963653664</v>
@@ -969,129 +993,135 @@
         <v>-0.169554384362192</v>
       </c>
       <c r="H4" t="n">
+        <v>-0.0184143242197956</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0.0181058995709713</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-0.278648268623139</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-0.37338220636912</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-0.204154783015747</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>-0.0837003183939476</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>-0.0988475340227592</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>-0.141210710616172</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>-0.0466720427614512</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>-0.0223308923262131</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0.0503303137154591</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
+        <v>-0.078711107427924</v>
+      </c>
+      <c r="T4" t="n">
         <v>-0.0794524172790022</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>-0.00749851703955117</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>-0.0732747438842462</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.114914367516149</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
+        <v>3.40883248308577</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>-0.00184761400226204</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>-0.0100046443402444</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>0.238507466780687</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>-0.0055179876751338</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>0.265749097758507</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>-3.63618198377684</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>1.08459192358979</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>1.08405563486571</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>1.69130769280195</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>2.74556373901538</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>0.75630921144054</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>2.08339580005781</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>-0.00656637404658737</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AM4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AN4" t="n">
         <v>-4.31875399729239</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AO4" t="n">
         <v>3.56540005694909</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AP4" t="n">
         <v>-0.782589675263861</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>-1.41801144666476</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AR4" t="n">
         <v>-42.063917768553</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AS4" t="n">
         <v>-0.0423580963653664</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AT4" t="n">
         <v>-0.0654341902052057</v>
       </c>
-      <c r="AR4" t="n">
-        <v>3.40883248308577</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AU4" t="n">
         <v>0.0988875903309765</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AV4" t="n">
         <v>-0.041946136308274</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AW4" t="n">
         <v>0.00639467520062348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" t="n">
         <v>-0.0480727916411618</v>
@@ -1112,129 +1142,135 @@
         <v>-0.114016310368139</v>
       </c>
       <c r="H5" t="n">
+        <v>-0.090581838971895</v>
+      </c>
+      <c r="I5" t="n">
         <v>-0.0943666974336294</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-0.046366232871423</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-0.130678648965293</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-0.048917726788189</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-0.0457414901501482</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-0.026573481692435</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-0.0692464942458135</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-0.0647205616522289</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>-0.0278724541611876</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>-0.0218776303200323</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
+        <v>-0.0670574800503381</v>
+      </c>
+      <c r="T5" t="n">
         <v>-0.0651659970916472</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>-0.094704517426158</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>-0.0662767394077226</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0296737136920025</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
+        <v>0.241745236060253</v>
+      </c>
+      <c r="Y5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Z5" t="n">
         <v>0.0108436371775343</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>0.0064511956297064</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>-0.240200751296639</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>-0.602380310114915</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>-0.239853211250507</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>12.8592769993275</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>-0.480525696225354</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>-0.491243416945087</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>-0.517661915067306</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
         <v>-0.268031660005875</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="n">
         <v>-0.416594915570839</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AK5" t="n">
         <v>-0.311494422645666</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AL5" t="n">
         <v>-0.0482426004035456</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
         <v>-3.27804295023073</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AO5" t="n">
         <v>0.103643179064499</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AP5" t="n">
         <v>-1.31587084830012</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.38010878600959</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AR5" t="n">
         <v>-6.61747476724499</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AS5" t="n">
         <v>-0.0480727916411618</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AT5" t="n">
         <v>-0.0889789398903094</v>
       </c>
-      <c r="AR5" t="n">
-        <v>0.241745236060253</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AU5" t="n">
         <v>-0.805735820374807</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AV5" t="n">
         <v>-0.0302881325843596</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AW5" t="n">
         <v>0.00829966907346026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" t="n">
         <v>0.00300839854680181</v>
@@ -1255,129 +1291,135 @@
         <v>0.0156302908688696</v>
       </c>
       <c r="H6" t="n">
+        <v>-0.0264330770365671</v>
+      </c>
+      <c r="I6" t="n">
         <v>-0.00777819389424965</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.183072132285433</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-0.0140515295826258</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.085549861147115</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.0722057873717832</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.0581279308629707</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.0594315464166114</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-0.0139516952096968</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.0972308094678789</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-0.0395915370136168</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
+        <v>0.0248045600792007</v>
+      </c>
+      <c r="T6" t="n">
         <v>0.0291116808889536</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>-0.0130612761644817</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0248295369766438</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>-0.0694984089622275</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
+        <v>-2.76898226499257</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>0.0145774880585199</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>-0.000123590283420022</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>-0.0748923204047765</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>-0.423678741868557</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>-0.0594431157486579</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>-2.61132807038946</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>0.137839947010808</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>0.13637941094463</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>-0.122399969203203</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
         <v>-0.388364951192247</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
         <v>-0.0224633016088872</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AK6" t="n">
         <v>-0.595670602562299</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AL6" t="n">
         <v>-0.0287033067680863</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AM6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AN6" t="n">
         <v>0.647163158559724</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AO6" t="n">
         <v>-3.1904011933925</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AP6" t="n">
         <v>-0.453595963951475</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="n">
         <v>0.622946781722748</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AR6" t="n">
         <v>-15.8994468340273</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AS6" t="n">
         <v>0.00300839854680181</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AT6" t="n">
         <v>-0.0879917342022967</v>
       </c>
-      <c r="AR6" t="n">
-        <v>-2.76898226499257</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AU6" t="n">
         <v>-0.190653634970529</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AV6" t="n">
         <v>0.0118321019448495</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AW6" t="n">
         <v>-0.00593181281709199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" t="n">
         <v>0.0677420175858707</v>
@@ -1398,129 +1440,135 @@
         <v>0.250285857549249</v>
       </c>
       <c r="H7" t="n">
+        <v>0.0988073686745112</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.0918115939259928</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.0601744798308835</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-0.188331569638821</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.0406597387657337</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.103548025235894</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.00202098858221799</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.0874935060532407</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.110979265869809</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.0239107660601627</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.00273469106055817</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>0.106006793938559</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.105554071475889</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.0951759245750315</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.111511245163811</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0276913164771287</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
+        <v>-1.36750673911582</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>-0.000652098137484839</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>-0.0064557992462484</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>-0.283628703906132</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>0.138826687668009</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>-0.309927730022684</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>-4.93482380993126</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.418246721515095</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>0.424361583032095</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>0.289059744010996</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
         <v>0.308994584925497</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="n">
         <v>0.159101834134017</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
         <v>0.197995368697023</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AL7" t="n">
         <v>-0.0626469474552824</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AM7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AN7" t="n">
         <v>1.12134033295021</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AO7" t="n">
         <v>-5.94298722785559</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AP7" t="n">
         <v>2.15545868450043</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
         <v>1.54602068082667</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AR7" t="n">
         <v>-32.1995523411849</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AS7" t="n">
         <v>0.0677420175858707</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AT7" t="n">
         <v>-0.130900303696153</v>
       </c>
-      <c r="AR7" t="n">
-        <v>-1.36750673911582</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AU7" t="n">
         <v>-0.563513299647262</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AV7" t="n">
         <v>-0.0501937303954304</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AW7" t="n">
         <v>-0.0185588523633794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" t="n">
         <v>0.051536860950639</v>
@@ -1541,129 +1589,135 @@
         <v>-0.11590073157777</v>
       </c>
       <c r="H8" t="n">
+        <v>-0.0400778613682788</v>
+      </c>
+      <c r="I8" t="n">
         <v>-0.0493917054781802</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-0.0883645155060498</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.309219299525867</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.0567337331081234</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-0.0715951342108236</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-0.0463280683589995</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.0138111941148235</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.0861825699207249</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.263100653547779</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>0.0241502037875185</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>0.0973588798247507</v>
+      </c>
+      <c r="T8" t="n">
         <v>0.0823716821161474</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>-0.0423401208623003</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0918117366690664</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.00189803511554691</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
+        <v>0.283112944514979</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>-0.00203471874096844</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>-0.00704514598014381</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>-0.0196716387334885</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>1.71905337412741</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
         <v>-0.0529446881570243</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>-9.01272307721351</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>-1.96214937859133</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>-1.89546618886632</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
         <v>-1.89651190208578</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AI8" t="n">
         <v>-1.22021097105653</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>-1.22631695627796</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AK8" t="n">
         <v>-0.810419476847576</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AL8" t="n">
         <v>-0.0360635327910034</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AM8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AN8" t="n">
         <v>11.0611048510848</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AO8" t="n">
         <v>-8.13657157043532</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AP8" t="n">
         <v>1.89965622981696</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
         <v>1.2231669853248</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AR8" t="n">
         <v>-14.3772288344109</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AS8" t="n">
         <v>0.051536860950639</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AT8" t="n">
         <v>0.623368914024887</v>
       </c>
-      <c r="AR8" t="n">
-        <v>0.283112944514979</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AU8" t="n">
         <v>0.868083983240932</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AV8" t="n">
         <v>0.103648576807794</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AW8" t="n">
         <v>-0.0301335771134524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0452802345411879</v>
@@ -1684,129 +1738,135 @@
         <v>0.153427391633997</v>
       </c>
       <c r="H9" t="n">
+        <v>0.0872449256177965</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.0855536155303945</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.0504734259398501</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-0.208271122741779</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.0986245611203094</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.067673495916023</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-0.0108437631294407</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.0786633420934962</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.0415623718171625</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-0.0324191136737228</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-0.0027053805893549</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>0.0353936440864668</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.0383287535447493</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.09066077539429</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>0.0416848994848347</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.0247461477456109</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
+        <v>-1.12932288721738</v>
+      </c>
+      <c r="Y9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>-0.000969293831558328</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>-0.00545927080555194</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>0.120325299563882</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>-0.314908419026853</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>0.0986064075879345</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>-0.624784079803963</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>1.05828541957378</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>1.06438261422827</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>0.785942009562261</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>0.487882730365099</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
         <v>0.697195612240213</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
         <v>-0.0374455911788562</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AL9" t="n">
         <v>-0.0315474910081037</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AM9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AN9" t="n">
         <v>-1.67028852900829</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AO9" t="n">
         <v>-0.0109312412913779</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AP9" t="n">
         <v>-0.191921675231057</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.336248048840461</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AR9" t="n">
         <v>-38.3424138223202</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AS9" t="n">
         <v>-0.0452802345411879</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AT9" t="n">
         <v>-0.085804112752481</v>
       </c>
-      <c r="AR9" t="n">
-        <v>-1.12932288721738</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AU9" t="n">
         <v>-0.56047013214129</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AV9" t="n">
         <v>-0.0496410442958685</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AW9" t="n">
         <v>0.000208184884516435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" t="n">
         <v>-0.00344133204854236</v>
@@ -1827,129 +1887,135 @@
         <v>0.0123800376221514</v>
       </c>
       <c r="H10" t="n">
+        <v>0.0517906362056633</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.0705558338791445</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.0849547857042242</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.0601430323680632</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.0292138845299469</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.108725795381303</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.0660182326205712</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.00620438066090511</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.0307882196430586</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-0.0506951096157239</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>0.013325731189545</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
+        <v>0.0243370745759228</v>
+      </c>
+      <c r="T10" t="n">
         <v>0.0325507305764863</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.0637311713530358</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.0274333514639498</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>-0.0338589119520969</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
+        <v>0.338891745096766</v>
+      </c>
+      <c r="Y10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>-0.00540575234929896</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>-0.00579879783185996</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-0.0342589796517672</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>-0.317730159419209</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
         <v>-0.0346914560561887</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AE10" t="n">
         <v>9.18564175834393</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AF10" t="n">
         <v>0.0993371854900619</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AG10" t="n">
         <v>0.0648298521035288</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AH10" t="n">
         <v>0.120572232824682</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AI10" t="n">
         <v>-0.117960350491315</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="n">
         <v>0.0824821535077846</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AK10" t="n">
         <v>0.322043412432475</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AL10" t="n">
         <v>-0.0161333980051841</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AM10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AN10" t="n">
         <v>-3.36054905774655</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AO10" t="n">
         <v>0.125640023711585</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AP10" t="n">
         <v>-1.05862112080309</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.969569942067806</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AR10" t="n">
         <v>20.4716391934634</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AS10" t="n">
         <v>-0.00344133204854236</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AT10" t="n">
         <v>-0.0682606175468987</v>
       </c>
-      <c r="AR10" t="n">
-        <v>0.338891745096766</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AU10" t="n">
         <v>0.255688366175892</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AV10" t="n">
         <v>0.000487602492993006</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AW10" t="n">
         <v>0.0154679259900934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" t="n">
         <v>0.0148543968445671</v>
@@ -1970,129 +2036,135 @@
         <v>-0.0663141535071389</v>
       </c>
       <c r="H11" t="n">
+        <v>0.0145209574776209</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.0296954906944263</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.0158617624856274</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.313060253546427</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-0.0427652547046527</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.0468517688481327</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.109958567821692</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.042769586516405</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.0211958266043548</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-0.0434899261813493</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>-0.000646349904212877</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
+        <v>0.0320732469906415</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.03321280075391</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.0240534255699838</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.0233233898465209</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>-0.134269002145114</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
+        <v>-1.60245407764797</v>
+      </c>
+      <c r="Y11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>0.0169332582755317</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>0.0533113040488226</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>-0.0354567410752362</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>0.128949509529747</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>-0.0422757744771231</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>6.42513956495643</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>-0.280465339930393</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>-0.315517269456471</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>-0.268724626977033</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>-0.489446482450284</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.198475120765655</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
         <v>-0.48313178901756</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AL11" t="n">
         <v>0.0595370092343964</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AM11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AN11" t="n">
         <v>-1.42640909208072</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AO11" t="n">
         <v>5.91211095973774</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AP11" t="n">
         <v>-0.895613718645758</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.823422918814776</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AR11" t="n">
         <v>64.7608500031866</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AS11" t="n">
         <v>0.0148543968445671</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AT11" t="n">
         <v>-0.0794686588701281</v>
       </c>
-      <c r="AR11" t="n">
-        <v>-1.60245407764797</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AU11" t="n">
         <v>0.482211586012499</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AV11" t="n">
         <v>0.0316327784762719</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AW11" t="n">
         <v>0.00888449742549417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12" t="n">
         <v>0.132144077720306</v>
@@ -2113,129 +2185,135 @@
         <v>-0.049942846229566</v>
       </c>
       <c r="H12" t="n">
+        <v>0.0692573002415602</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.0663592388653425</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.12082021118173</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.467253145695357</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.0122705756134747</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.0523986716894069</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.131205113193585</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.198025239949699</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.0571106148616265</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-0.00197631555638445</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0.0331111192044257</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
+        <v>0.0984531138090642</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.094141686407852</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0506071158844021</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.0855989607660336</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>-0.193983119750397</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
+        <v>-0.456645557777998</v>
+      </c>
+      <c r="Y12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>-0.0158690518044377</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>-0.00954756689330399</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>0.10215117539764</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>1.02430888453424</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>0.0779898973230106</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>10.3825789897294</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>-1.96187907500934</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>-1.89482506440636</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>-1.59565512176468</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
         <v>-1.18205595693551</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="n">
         <v>-1.22766947552045</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
         <v>-1.35410658786014</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AL12" t="n">
         <v>0.168168106349812</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AM12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AN12" t="n">
         <v>4.24082559502784</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AO12" t="n">
         <v>6.72187461778694</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AP12" t="n">
         <v>3.20570944017448</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
         <v>1.13064796511604</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AR12" t="n">
         <v>69.5078139826724</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AS12" t="n">
         <v>0.132144077720306</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AT12" t="n">
         <v>0.0495522387392417</v>
       </c>
-      <c r="AR12" t="n">
-        <v>-0.456645557777998</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AU12" t="n">
         <v>1.25678752951199</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AV12" t="n">
         <v>0.0696894773037612</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AW12" t="n">
         <v>0.0122694085372572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" t="n">
         <v>-0.0608450885043526</v>
@@ -2256,123 +2334,129 @@
         <v>-0.0508814655739771</v>
       </c>
       <c r="H13" t="n">
+        <v>-0.110037912279872</v>
+      </c>
+      <c r="I13" t="n">
         <v>-0.133451925871853</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-0.237554391414924</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-0.170995817172662</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-0.162021848639044</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-0.181026454047777</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-0.123243924866692</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-0.186937087540904</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-0.116101471196711</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-0.146379752900888</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-0.0352814659320229</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>-0.171820423703977</v>
+      </c>
+      <c r="T13" t="n">
         <v>-0.172749983022184</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>-0.127267221710903</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>-0.16932861076034</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.187571632441963</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
+        <v>3.29827503179176</v>
+      </c>
+      <c r="Y13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>-0.00388917318968417</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>-0.010783841722055</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>0.10029056827084</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>-0.63488960520175</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
         <v>0.129596173698853</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
         <v>-8.88016008611467</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AF13" t="n">
         <v>1.06512778425032</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>1.04478329645459</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AH13" t="n">
         <v>1.2436250193625</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AI13" t="n">
         <v>1.07400427593327</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
         <v>0.837274531912688</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AK13" t="n">
         <v>1.8697104870729</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AL13" t="n">
         <v>0.010749126320787</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AM13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AN13" t="n">
         <v>-3.68921628388639</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AO13" t="n">
         <v>2.44971914892797</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AP13" t="n">
         <v>-0.698329443036231</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.587401204304756</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AR13" t="n">
         <v>-10.837588555778</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AS13" t="n">
         <v>-0.0608450885043526</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AT13" t="n">
         <v>-0.0127727968714012</v>
       </c>
-      <c r="AR13" t="n">
-        <v>3.29827503179176</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
         <v>-0.513037522362324</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AV13" t="n">
         <v>-0.0347804888684874</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AW13" t="n">
         <v>-0.00141794201922911</v>
       </c>
     </row>
